--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T14:30:40+00:00</t>
+    <t>2024-12-13T08:39:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA (https://www.elga.gv.at/)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-verdachtArbeitsSchuelerunfall.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MOPEDAccount#Account</t>
+    <t>element:http://example.org/StructureDefinition/MopedAccount#Account</t>
   </si>
   <si>
     <t>ID</t>
